--- a/artfynd/A 9093-2025 artfynd.xlsx
+++ b/artfynd/A 9093-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>106170769</v>
       </c>
       <c r="B2" t="n">
-        <v>56395</v>
+        <v>57478</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>800500.5737911831</v>
+        <v>800500</v>
       </c>
       <c r="R2" t="n">
-        <v>7176753.539433044</v>
+        <v>7176753</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,19 +756,9 @@
           <t>2019-08-07</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2019-08-07</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -918,6 +908,121 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>122962305</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57494</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Södra Bergfors, Vb</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>800563</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7176677</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Bureå</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2019-08-07</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2019-08-07</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>både färska och äldre hack i granar</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 9093-2025 artfynd.xlsx
+++ b/artfynd/A 9093-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1023,6 +1023,571 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>123328272</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57494</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Bureberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>800517</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7176634</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Bureå</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>hack i gammal torraka</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>123327889</v>
+      </c>
+      <c r="B6" t="n">
+        <v>78798</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>185</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Bureberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>800568</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7176666</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Bureå</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>123327996</v>
+      </c>
+      <c r="B7" t="n">
+        <v>90952</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Bureberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>800530</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7176618</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Bureå</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>123327937</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57494</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Bureberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>800548</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7176632</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Bureå</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>hack i gammal låga</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>123327865</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57494</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Bureberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>800466</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7176708</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Bureå</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>hålhack i talltorraka</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 9093-2025 artfynd.xlsx
+++ b/artfynd/A 9093-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>106170769</v>
       </c>
       <c r="B2" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>122962305</v>
       </c>
       <c r="B4" t="n">
-        <v>57494</v>
+        <v>57497</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1025,10 +1025,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123328272</v>
+        <v>123327937</v>
       </c>
       <c r="B5" t="n">
-        <v>57494</v>
+        <v>57497</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1073,10 +1073,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>800517</v>
+        <v>800548</v>
       </c>
       <c r="R5" t="n">
-        <v>7176634</v>
+        <v>7176632</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1113,7 +1113,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>hack i gammal torraka</t>
+          <t>hack i gammal låga</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1143,7 +1143,7 @@
         <v>123327889</v>
       </c>
       <c r="B6" t="n">
-        <v>78798</v>
+        <v>78801</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>123327996</v>
       </c>
       <c r="B7" t="n">
-        <v>90952</v>
+        <v>90955</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1360,10 +1360,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123327937</v>
+        <v>123328272</v>
       </c>
       <c r="B8" t="n">
-        <v>57494</v>
+        <v>57497</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>800548</v>
+        <v>800517</v>
       </c>
       <c r="R8" t="n">
-        <v>7176632</v>
+        <v>7176634</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1448,7 +1448,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>hack i gammal låga</t>
+          <t>hack i gammal torraka</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1478,7 +1478,7 @@
         <v>123327865</v>
       </c>
       <c r="B9" t="n">
-        <v>57494</v>
+        <v>57497</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1587,6 +1587,1030 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>123441457</v>
+      </c>
+      <c r="B10" t="n">
+        <v>5173</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Bureberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>800660</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7176636</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Bureå</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>breda gångar i granlåga</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>123441144</v>
+      </c>
+      <c r="B11" t="n">
+        <v>5173</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Bureberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>800585</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7176730</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Bureå</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>breda gnagspår i död gran</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>123441038</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57497</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Bureberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>800415</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7176760</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Bureå</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>hack i död gran</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>123441175</v>
+      </c>
+      <c r="B13" t="n">
+        <v>90975</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Bureberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>800571</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7176723</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Bureå</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>123441081</v>
+      </c>
+      <c r="B14" t="n">
+        <v>90957</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Bureberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>800526</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7176769</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Bureå</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>vidväxt på högstubbe av gran</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>123441000</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57497</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Bureberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>800417</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7176768</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Bureå</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>hack i torraka</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>123441111</v>
+      </c>
+      <c r="B16" t="n">
+        <v>78771</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Bureberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>800589</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7176762</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Bureå</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>123441387</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57481</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Bureberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>800647</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7176653</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Bureå</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>123441364</v>
+      </c>
+      <c r="B18" t="n">
+        <v>90922</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Bureberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>800644</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7176654</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Bureå</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 9093-2025 artfynd.xlsx
+++ b/artfynd/A 9093-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1025,10 +1025,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123327937</v>
+        <v>123327889</v>
       </c>
       <c r="B5" t="n">
-        <v>57497</v>
+        <v>78803</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1041,31 +1041,30 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>185</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1073,10 +1072,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>800548</v>
+        <v>800568</v>
       </c>
       <c r="R5" t="n">
-        <v>7176632</v>
+        <v>7176666</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1111,17 +1110,13 @@
           <t>2025-03-14</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>hack i gammal låga</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1140,10 +1135,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123327889</v>
+        <v>123327996</v>
       </c>
       <c r="B6" t="n">
-        <v>78801</v>
+        <v>90957</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1156,27 +1151,27 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>185</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -1187,10 +1182,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>800568</v>
+        <v>800530</v>
       </c>
       <c r="R6" t="n">
-        <v>7176666</v>
+        <v>7176618</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1250,10 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123327996</v>
+        <v>123328272</v>
       </c>
       <c r="B7" t="n">
-        <v>90955</v>
+        <v>57497</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1266,30 +1261,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1297,10 +1293,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>800530</v>
+        <v>800517</v>
       </c>
       <c r="R7" t="n">
-        <v>7176618</v>
+        <v>7176634</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1335,13 +1331,17 @@
           <t>2025-03-14</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>hack i gammal torraka</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1360,7 +1360,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123328272</v>
+        <v>123327937</v>
       </c>
       <c r="B8" t="n">
         <v>57497</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>800517</v>
+        <v>800548</v>
       </c>
       <c r="R8" t="n">
-        <v>7176634</v>
+        <v>7176632</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1448,7 +1448,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>hack i gammal torraka</t>
+          <t>hack i gammal låga</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1590,10 +1590,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123441457</v>
+        <v>123441387</v>
       </c>
       <c r="B10" t="n">
-        <v>5173</v>
+        <v>57481</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1602,34 +1602,33 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100526</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1639,10 +1638,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>800660</v>
+        <v>800647</v>
       </c>
       <c r="R10" t="n">
-        <v>7176636</v>
+        <v>7176653</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1679,7 +1678,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>breda gångar i granlåga</t>
+          <t>barksprätt på gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1688,7 +1687,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1707,10 +1705,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123441144</v>
+        <v>123441364</v>
       </c>
       <c r="B11" t="n">
-        <v>5173</v>
+        <v>90922</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1723,32 +1721,30 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100526</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1756,10 +1752,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>800585</v>
+        <v>800644</v>
       </c>
       <c r="R11" t="n">
-        <v>7176730</v>
+        <v>7176654</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1792,11 +1788,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>breda gnagspår i död gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1824,10 +1815,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123441038</v>
+        <v>123441081</v>
       </c>
       <c r="B12" t="n">
-        <v>57497</v>
+        <v>90957</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1840,31 +1831,30 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1872,10 +1862,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>800415</v>
+        <v>800526</v>
       </c>
       <c r="R12" t="n">
-        <v>7176760</v>
+        <v>7176769</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1912,7 +1902,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>hack i död gran</t>
+          <t>vidväxt på högstubbe av gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1921,6 +1911,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2049,10 +2040,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123441081</v>
+        <v>123441000</v>
       </c>
       <c r="B14" t="n">
-        <v>90957</v>
+        <v>57497</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2065,30 +2056,31 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2096,10 +2088,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>800526</v>
+        <v>800417</v>
       </c>
       <c r="R14" t="n">
-        <v>7176769</v>
+        <v>7176768</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2136,7 +2128,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>vidväxt på högstubbe av gran</t>
+          <t>hack i torraka</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2145,7 +2137,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2164,10 +2155,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123441000</v>
+        <v>123441144</v>
       </c>
       <c r="B15" t="n">
-        <v>57497</v>
+        <v>5173</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2176,33 +2167,34 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2212,10 +2204,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>800417</v>
+        <v>800585</v>
       </c>
       <c r="R15" t="n">
-        <v>7176768</v>
+        <v>7176730</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2252,7 +2244,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>hack i torraka</t>
+          <t>breda gnagspår i död gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2261,6 +2253,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2279,10 +2272,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123441111</v>
+        <v>123441038</v>
       </c>
       <c r="B16" t="n">
-        <v>78771</v>
+        <v>57497</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2295,30 +2288,31 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2326,10 +2320,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>800589</v>
+        <v>800415</v>
       </c>
       <c r="R16" t="n">
-        <v>7176762</v>
+        <v>7176760</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2364,13 +2358,17 @@
           <t>2025-03-21</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>hack i död gran</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2389,10 +2387,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123441387</v>
+        <v>123441457</v>
       </c>
       <c r="B17" t="n">
-        <v>57481</v>
+        <v>5173</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2401,33 +2399,34 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>100526</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2437,10 +2436,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>800647</v>
+        <v>800660</v>
       </c>
       <c r="R17" t="n">
-        <v>7176653</v>
+        <v>7176636</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2477,7 +2476,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>barksprätt på gran</t>
+          <t>breda gångar i granlåga</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2486,6 +2485,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2504,10 +2504,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123441364</v>
+        <v>123441111</v>
       </c>
       <c r="B18" t="n">
-        <v>90922</v>
+        <v>78771</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2516,31 +2516,31 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -2551,10 +2551,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>800644</v>
+        <v>800589</v>
       </c>
       <c r="R18" t="n">
-        <v>7176654</v>
+        <v>7176762</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2611,6 +2611,121 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>123452603</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57634</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>bobygge</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Bureberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>800571</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7176723</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Bureå</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>litet bohål ca 3cm brett och 2,5cm högt ca 2m upp på stammen av gammal rötad gran angripen av granticka.</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 9093-2025 artfynd.xlsx
+++ b/artfynd/A 9093-2025 artfynd.xlsx
@@ -1025,10 +1025,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123327889</v>
+        <v>123328272</v>
       </c>
       <c r="B5" t="n">
-        <v>78803</v>
+        <v>57497</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1041,30 +1041,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>185</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1072,10 +1073,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>800568</v>
+        <v>800517</v>
       </c>
       <c r="R5" t="n">
-        <v>7176666</v>
+        <v>7176634</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1110,13 +1111,17 @@
           <t>2025-03-14</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>hack i gammal torraka</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1135,10 +1140,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123327996</v>
+        <v>123327889</v>
       </c>
       <c r="B6" t="n">
-        <v>90957</v>
+        <v>78804</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1151,27 +1156,27 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>185</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -1182,10 +1187,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>800530</v>
+        <v>800568</v>
       </c>
       <c r="R6" t="n">
-        <v>7176618</v>
+        <v>7176666</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1245,7 +1250,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123328272</v>
+        <v>123327937</v>
       </c>
       <c r="B7" t="n">
         <v>57497</v>
@@ -1293,10 +1298,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>800517</v>
+        <v>800548</v>
       </c>
       <c r="R7" t="n">
-        <v>7176634</v>
+        <v>7176632</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1333,7 +1338,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>hack i gammal torraka</t>
+          <t>hack i gammal låga</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1360,7 +1365,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123327937</v>
+        <v>123327865</v>
       </c>
       <c r="B8" t="n">
         <v>57497</v>
@@ -1408,10 +1413,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>800548</v>
+        <v>800466</v>
       </c>
       <c r="R8" t="n">
-        <v>7176632</v>
+        <v>7176708</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1448,7 +1453,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>hack i gammal låga</t>
+          <t>hålhack i talltorraka</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1475,10 +1480,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123327865</v>
+        <v>123327996</v>
       </c>
       <c r="B9" t="n">
-        <v>57497</v>
+        <v>90963</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1491,31 +1496,30 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1523,10 +1527,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>800466</v>
+        <v>800530</v>
       </c>
       <c r="R9" t="n">
-        <v>7176708</v>
+        <v>7176618</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1561,17 +1565,13 @@
           <t>2025-03-14</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>hålhack i talltorraka</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1590,10 +1590,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123441387</v>
+        <v>123441000</v>
       </c>
       <c r="B10" t="n">
-        <v>57481</v>
+        <v>57497</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1606,16 +1606,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1628,7 +1628,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1638,10 +1638,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>800647</v>
+        <v>800417</v>
       </c>
       <c r="R10" t="n">
-        <v>7176653</v>
+        <v>7176768</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1678,7 +1678,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>barksprätt på gran</t>
+          <t>hack i torraka</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1705,10 +1705,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123441364</v>
+        <v>123441387</v>
       </c>
       <c r="B11" t="n">
-        <v>90922</v>
+        <v>57481</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1717,34 +1717,35 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1752,10 +1753,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>800644</v>
+        <v>800647</v>
       </c>
       <c r="R11" t="n">
-        <v>7176654</v>
+        <v>7176653</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1790,13 +1791,17 @@
           <t>2025-03-21</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1815,10 +1820,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123441081</v>
+        <v>123441144</v>
       </c>
       <c r="B12" t="n">
-        <v>90957</v>
+        <v>5173</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1827,34 +1832,36 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1862,10 +1869,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>800526</v>
+        <v>800585</v>
       </c>
       <c r="R12" t="n">
-        <v>7176769</v>
+        <v>7176730</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1902,7 +1909,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>vidväxt på högstubbe av gran</t>
+          <t>breda gnagspår i död gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1930,10 +1937,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123441175</v>
+        <v>123441038</v>
       </c>
       <c r="B13" t="n">
-        <v>90975</v>
+        <v>57497</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1946,30 +1953,31 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1977,10 +1985,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>800571</v>
+        <v>800415</v>
       </c>
       <c r="R13" t="n">
-        <v>7176723</v>
+        <v>7176760</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2015,13 +2023,17 @@
           <t>2025-03-21</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>hack i död gran</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2040,10 +2052,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123441000</v>
+        <v>123441081</v>
       </c>
       <c r="B14" t="n">
-        <v>57497</v>
+        <v>90963</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2056,31 +2068,30 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2088,10 +2099,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>800417</v>
+        <v>800526</v>
       </c>
       <c r="R14" t="n">
-        <v>7176768</v>
+        <v>7176769</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2128,7 +2139,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>hack i torraka</t>
+          <t>vidväxt på högstubbe av gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2137,6 +2148,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2155,10 +2167,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123441144</v>
+        <v>123441364</v>
       </c>
       <c r="B15" t="n">
-        <v>5173</v>
+        <v>90928</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2171,32 +2183,30 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100526</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2204,10 +2214,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>800585</v>
+        <v>800644</v>
       </c>
       <c r="R15" t="n">
-        <v>7176730</v>
+        <v>7176654</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2240,11 +2250,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>breda gnagspår i död gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2272,10 +2277,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123441038</v>
+        <v>123441175</v>
       </c>
       <c r="B16" t="n">
-        <v>57497</v>
+        <v>90981</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2288,31 +2293,30 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2320,10 +2324,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>800415</v>
+        <v>800571</v>
       </c>
       <c r="R16" t="n">
-        <v>7176760</v>
+        <v>7176723</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2358,17 +2362,13 @@
           <t>2025-03-21</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>hack i död gran</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2507,7 +2507,7 @@
         <v>123441111</v>
       </c>
       <c r="B18" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>

--- a/artfynd/A 9093-2025 artfynd.xlsx
+++ b/artfynd/A 9093-2025 artfynd.xlsx
@@ -1025,10 +1025,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123328272</v>
+        <v>123327996</v>
       </c>
       <c r="B5" t="n">
-        <v>57497</v>
+        <v>90966</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1041,31 +1041,30 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1073,10 +1072,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>800517</v>
+        <v>800530</v>
       </c>
       <c r="R5" t="n">
-        <v>7176634</v>
+        <v>7176618</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1111,17 +1110,13 @@
           <t>2025-03-14</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>hack i gammal torraka</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1140,10 +1135,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123327889</v>
+        <v>123327865</v>
       </c>
       <c r="B6" t="n">
-        <v>78804</v>
+        <v>57497</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1156,30 +1151,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>185</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1187,10 +1183,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>800568</v>
+        <v>800466</v>
       </c>
       <c r="R6" t="n">
-        <v>7176666</v>
+        <v>7176708</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1225,13 +1221,17 @@
           <t>2025-03-14</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>hålhack i talltorraka</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1250,7 +1250,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123327937</v>
+        <v>123328272</v>
       </c>
       <c r="B7" t="n">
         <v>57497</v>
@@ -1298,10 +1298,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>800548</v>
+        <v>800517</v>
       </c>
       <c r="R7" t="n">
-        <v>7176632</v>
+        <v>7176634</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1338,7 +1338,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>hack i gammal låga</t>
+          <t>hack i gammal torraka</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1365,7 +1365,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123327865</v>
+        <v>123327937</v>
       </c>
       <c r="B8" t="n">
         <v>57497</v>
@@ -1413,10 +1413,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>800466</v>
+        <v>800548</v>
       </c>
       <c r="R8" t="n">
-        <v>7176708</v>
+        <v>7176632</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1453,7 +1453,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>hålhack i talltorraka</t>
+          <t>hack i gammal låga</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1480,10 +1480,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123327996</v>
+        <v>123327889</v>
       </c>
       <c r="B9" t="n">
-        <v>90963</v>
+        <v>78807</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1496,27 +1496,27 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>185</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -1527,10 +1527,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>800530</v>
+        <v>800568</v>
       </c>
       <c r="R9" t="n">
-        <v>7176618</v>
+        <v>7176666</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1590,10 +1590,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123441000</v>
+        <v>123441081</v>
       </c>
       <c r="B10" t="n">
-        <v>57497</v>
+        <v>90966</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1606,31 +1606,30 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1638,10 +1637,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>800417</v>
+        <v>800526</v>
       </c>
       <c r="R10" t="n">
-        <v>7176768</v>
+        <v>7176769</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1678,7 +1677,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>hack i torraka</t>
+          <t>vidväxt på högstubbe av gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1687,6 +1686,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1705,10 +1705,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123441387</v>
+        <v>123441457</v>
       </c>
       <c r="B11" t="n">
-        <v>57481</v>
+        <v>5173</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1717,33 +1717,34 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>100526</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1753,10 +1754,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>800647</v>
+        <v>800660</v>
       </c>
       <c r="R11" t="n">
-        <v>7176653</v>
+        <v>7176636</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1793,7 +1794,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>barksprätt på gran</t>
+          <t>breda gångar i granlåga</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1802,6 +1803,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1820,10 +1822,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123441144</v>
+        <v>123441111</v>
       </c>
       <c r="B12" t="n">
-        <v>5173</v>
+        <v>78775</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1832,36 +1834,34 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1869,10 +1869,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>800585</v>
+        <v>800589</v>
       </c>
       <c r="R12" t="n">
-        <v>7176730</v>
+        <v>7176762</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1905,11 +1905,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>breda gnagspår i död gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1937,10 +1932,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123441038</v>
+        <v>123441175</v>
       </c>
       <c r="B13" t="n">
-        <v>57497</v>
+        <v>90984</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1953,31 +1948,30 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1985,10 +1979,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>800415</v>
+        <v>800571</v>
       </c>
       <c r="R13" t="n">
-        <v>7176760</v>
+        <v>7176723</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2023,17 +2017,13 @@
           <t>2025-03-21</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>hack i död gran</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2052,10 +2042,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123441081</v>
+        <v>123441000</v>
       </c>
       <c r="B14" t="n">
-        <v>90963</v>
+        <v>57497</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2068,30 +2058,31 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2099,10 +2090,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>800526</v>
+        <v>800417</v>
       </c>
       <c r="R14" t="n">
-        <v>7176769</v>
+        <v>7176768</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2139,7 +2130,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>vidväxt på högstubbe av gran</t>
+          <t>hack i torraka</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2148,7 +2139,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2167,10 +2157,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123441364</v>
+        <v>123441144</v>
       </c>
       <c r="B15" t="n">
-        <v>90928</v>
+        <v>5173</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2183,30 +2173,32 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>100526</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2214,10 +2206,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>800644</v>
+        <v>800585</v>
       </c>
       <c r="R15" t="n">
-        <v>7176654</v>
+        <v>7176730</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2250,6 +2242,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>breda gnagspår i död gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2277,10 +2274,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123441175</v>
+        <v>123441364</v>
       </c>
       <c r="B16" t="n">
-        <v>90981</v>
+        <v>90931</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2289,25 +2286,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2324,10 +2321,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>800571</v>
+        <v>800644</v>
       </c>
       <c r="R16" t="n">
-        <v>7176723</v>
+        <v>7176654</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2387,10 +2384,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123441457</v>
+        <v>123441038</v>
       </c>
       <c r="B17" t="n">
-        <v>5173</v>
+        <v>57497</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2399,34 +2396,33 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2436,10 +2432,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>800660</v>
+        <v>800415</v>
       </c>
       <c r="R17" t="n">
-        <v>7176636</v>
+        <v>7176760</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2476,7 +2472,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>breda gångar i granlåga</t>
+          <t>hack i död gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2485,7 +2481,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2504,10 +2499,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123441111</v>
+        <v>123441387</v>
       </c>
       <c r="B18" t="n">
-        <v>78772</v>
+        <v>57481</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2520,30 +2515,31 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2551,10 +2547,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>800589</v>
+        <v>800647</v>
       </c>
       <c r="R18" t="n">
-        <v>7176762</v>
+        <v>7176653</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2589,13 +2585,17 @@
           <t>2025-03-21</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 9093-2025 artfynd.xlsx
+++ b/artfynd/A 9093-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>106170769</v>
       </c>
       <c r="B2" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>122962305</v>
       </c>
       <c r="B4" t="n">
-        <v>57497</v>
+        <v>57503</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1025,10 +1025,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123327996</v>
+        <v>123327865</v>
       </c>
       <c r="B5" t="n">
-        <v>90966</v>
+        <v>57503</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1041,30 +1041,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1072,10 +1073,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>800530</v>
+        <v>800466</v>
       </c>
       <c r="R5" t="n">
-        <v>7176618</v>
+        <v>7176708</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1110,13 +1111,17 @@
           <t>2025-03-14</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>hålhack i talltorraka</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1135,10 +1140,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123327865</v>
+        <v>123327996</v>
       </c>
       <c r="B6" t="n">
-        <v>57497</v>
+        <v>90983</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1151,31 +1156,30 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1183,10 +1187,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>800466</v>
+        <v>800530</v>
       </c>
       <c r="R6" t="n">
-        <v>7176708</v>
+        <v>7176618</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1221,17 +1225,13 @@
           <t>2025-03-14</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>hålhack i talltorraka</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1253,7 +1253,7 @@
         <v>123328272</v>
       </c>
       <c r="B7" t="n">
-        <v>57497</v>
+        <v>57503</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1365,10 +1365,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123327937</v>
+        <v>123327889</v>
       </c>
       <c r="B8" t="n">
-        <v>57497</v>
+        <v>78813</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1381,31 +1381,30 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>185</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1413,10 +1412,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>800548</v>
+        <v>800568</v>
       </c>
       <c r="R8" t="n">
-        <v>7176632</v>
+        <v>7176666</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1451,17 +1450,13 @@
           <t>2025-03-14</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>hack i gammal låga</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1480,10 +1475,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123327889</v>
+        <v>123327937</v>
       </c>
       <c r="B9" t="n">
-        <v>78807</v>
+        <v>57503</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1496,30 +1491,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>185</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1527,10 +1523,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>800568</v>
+        <v>800548</v>
       </c>
       <c r="R9" t="n">
-        <v>7176666</v>
+        <v>7176632</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1565,13 +1561,17 @@
           <t>2025-03-14</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>hack i gammal låga</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1590,10 +1590,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123441081</v>
+        <v>123441457</v>
       </c>
       <c r="B10" t="n">
-        <v>90966</v>
+        <v>5174</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1602,34 +1602,36 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1637,10 +1639,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>800526</v>
+        <v>800660</v>
       </c>
       <c r="R10" t="n">
-        <v>7176769</v>
+        <v>7176636</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1677,7 +1679,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>vidväxt på högstubbe av gran</t>
+          <t>breda gångar i granlåga</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1705,10 +1707,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123441457</v>
+        <v>123441111</v>
       </c>
       <c r="B11" t="n">
-        <v>5173</v>
+        <v>78781</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1717,36 +1719,34 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1754,10 +1754,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>800660</v>
+        <v>800589</v>
       </c>
       <c r="R11" t="n">
-        <v>7176636</v>
+        <v>7176762</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1790,11 +1790,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>breda gångar i granlåga</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1822,10 +1817,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123441111</v>
+        <v>123441175</v>
       </c>
       <c r="B12" t="n">
-        <v>78775</v>
+        <v>91001</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1838,27 +1833,27 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1869,10 +1864,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>800589</v>
+        <v>800571</v>
       </c>
       <c r="R12" t="n">
-        <v>7176762</v>
+        <v>7176723</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1932,10 +1927,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123441175</v>
+        <v>123441144</v>
       </c>
       <c r="B13" t="n">
-        <v>90984</v>
+        <v>5174</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1944,34 +1939,36 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>100526</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1979,10 +1976,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>800571</v>
+        <v>800585</v>
       </c>
       <c r="R13" t="n">
-        <v>7176723</v>
+        <v>7176730</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2015,6 +2012,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>breda gnagspår i död gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2045,7 +2047,7 @@
         <v>123441000</v>
       </c>
       <c r="B14" t="n">
-        <v>57497</v>
+        <v>57503</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2157,10 +2159,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123441144</v>
+        <v>123441038</v>
       </c>
       <c r="B15" t="n">
-        <v>5173</v>
+        <v>57503</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2169,34 +2171,33 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2206,10 +2207,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>800585</v>
+        <v>800415</v>
       </c>
       <c r="R15" t="n">
-        <v>7176730</v>
+        <v>7176760</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2246,7 +2247,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>breda gnagspår i död gran</t>
+          <t>hack i död gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2255,7 +2256,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2274,10 +2274,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123441364</v>
+        <v>123441081</v>
       </c>
       <c r="B16" t="n">
-        <v>90931</v>
+        <v>90983</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2286,25 +2286,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2321,10 +2321,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>800644</v>
+        <v>800526</v>
       </c>
       <c r="R16" t="n">
-        <v>7176654</v>
+        <v>7176769</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2357,6 +2357,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>vidväxt på högstubbe av gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2384,10 +2389,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123441038</v>
+        <v>123441387</v>
       </c>
       <c r="B17" t="n">
-        <v>57497</v>
+        <v>57487</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2400,16 +2405,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2422,7 +2427,7 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2432,10 +2437,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>800415</v>
+        <v>800647</v>
       </c>
       <c r="R17" t="n">
-        <v>7176760</v>
+        <v>7176653</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2472,7 +2477,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>hack i död gran</t>
+          <t>barksprätt på gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2499,10 +2504,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123441387</v>
+        <v>123441364</v>
       </c>
       <c r="B18" t="n">
-        <v>57481</v>
+        <v>90948</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2511,35 +2516,34 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2547,10 +2551,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>800647</v>
+        <v>800644</v>
       </c>
       <c r="R18" t="n">
-        <v>7176653</v>
+        <v>7176654</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2585,17 +2589,13 @@
           <t>2025-03-21</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>barksprätt på gran</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2617,7 +2617,7 @@
         <v>123452603</v>
       </c>
       <c r="B19" t="n">
-        <v>57634</v>
+        <v>57640</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>

--- a/artfynd/A 9093-2025 artfynd.xlsx
+++ b/artfynd/A 9093-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>106170769</v>
       </c>
       <c r="B2" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>123327865</v>
       </c>
       <c r="B5" t="n">
-        <v>57503</v>
+        <v>57506</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1140,10 +1140,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123327996</v>
+        <v>123328272</v>
       </c>
       <c r="B6" t="n">
-        <v>90983</v>
+        <v>57506</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1156,30 +1156,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1187,10 +1188,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>800530</v>
+        <v>800517</v>
       </c>
       <c r="R6" t="n">
-        <v>7176618</v>
+        <v>7176634</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1225,13 +1226,17 @@
           <t>2025-03-14</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>hack i gammal torraka</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1250,10 +1255,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123328272</v>
+        <v>123327889</v>
       </c>
       <c r="B7" t="n">
-        <v>57503</v>
+        <v>78818</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1266,31 +1271,30 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>185</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1298,10 +1302,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>800517</v>
+        <v>800568</v>
       </c>
       <c r="R7" t="n">
-        <v>7176634</v>
+        <v>7176666</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1336,17 +1340,13 @@
           <t>2025-03-14</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>hack i gammal torraka</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1365,10 +1365,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123327889</v>
+        <v>123327996</v>
       </c>
       <c r="B8" t="n">
-        <v>78813</v>
+        <v>90988</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1381,27 +1381,27 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>185</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -1412,10 +1412,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>800568</v>
+        <v>800530</v>
       </c>
       <c r="R8" t="n">
-        <v>7176666</v>
+        <v>7176618</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1478,7 +1478,7 @@
         <v>123327937</v>
       </c>
       <c r="B9" t="n">
-        <v>57503</v>
+        <v>57506</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123441457</v>
+        <v>123441000</v>
       </c>
       <c r="B10" t="n">
-        <v>5174</v>
+        <v>57506</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1602,34 +1602,33 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1639,10 +1638,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>800660</v>
+        <v>800417</v>
       </c>
       <c r="R10" t="n">
-        <v>7176636</v>
+        <v>7176768</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1679,7 +1678,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>breda gångar i granlåga</t>
+          <t>hack i torraka</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1688,7 +1687,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1710,7 +1708,7 @@
         <v>123441111</v>
       </c>
       <c r="B11" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1817,10 +1815,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123441175</v>
+        <v>123441457</v>
       </c>
       <c r="B12" t="n">
-        <v>91001</v>
+        <v>5176</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1829,34 +1827,36 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>100526</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1864,10 +1864,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>800571</v>
+        <v>800660</v>
       </c>
       <c r="R12" t="n">
-        <v>7176723</v>
+        <v>7176636</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1900,6 +1900,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>breda gångar i granlåga</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1927,10 +1932,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123441144</v>
+        <v>123441175</v>
       </c>
       <c r="B13" t="n">
-        <v>5174</v>
+        <v>91006</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1939,36 +1944,34 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100526</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1976,10 +1979,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>800585</v>
+        <v>800571</v>
       </c>
       <c r="R13" t="n">
-        <v>7176730</v>
+        <v>7176723</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2012,11 +2015,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>breda gnagspår i död gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2044,10 +2042,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123441000</v>
+        <v>123441038</v>
       </c>
       <c r="B14" t="n">
-        <v>57503</v>
+        <v>57506</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2092,10 +2090,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>800417</v>
+        <v>800415</v>
       </c>
       <c r="R14" t="n">
-        <v>7176768</v>
+        <v>7176760</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2132,7 +2130,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>hack i torraka</t>
+          <t>hack i död gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2159,10 +2157,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123441038</v>
+        <v>123441364</v>
       </c>
       <c r="B15" t="n">
-        <v>57503</v>
+        <v>90953</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2171,35 +2169,34 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2207,10 +2204,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>800415</v>
+        <v>800644</v>
       </c>
       <c r="R15" t="n">
-        <v>7176760</v>
+        <v>7176654</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2245,17 +2242,13 @@
           <t>2025-03-21</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>hack i död gran</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2274,10 +2267,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123441081</v>
+        <v>123441387</v>
       </c>
       <c r="B16" t="n">
-        <v>90983</v>
+        <v>57490</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2290,30 +2283,31 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2321,10 +2315,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>800526</v>
+        <v>800647</v>
       </c>
       <c r="R16" t="n">
-        <v>7176769</v>
+        <v>7176653</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2361,7 +2355,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>vidväxt på högstubbe av gran</t>
+          <t>barksprätt på gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2370,7 +2364,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2389,10 +2382,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123441387</v>
+        <v>123441144</v>
       </c>
       <c r="B17" t="n">
-        <v>57487</v>
+        <v>5176</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2401,33 +2394,34 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>100526</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2437,10 +2431,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>800647</v>
+        <v>800585</v>
       </c>
       <c r="R17" t="n">
-        <v>7176653</v>
+        <v>7176730</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2477,7 +2471,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>barksprätt på gran</t>
+          <t>breda gnagspår i död gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2486,6 +2480,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2504,10 +2499,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123441364</v>
+        <v>123441081</v>
       </c>
       <c r="B18" t="n">
-        <v>90948</v>
+        <v>90988</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2516,25 +2511,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2551,10 +2546,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>800644</v>
+        <v>800526</v>
       </c>
       <c r="R18" t="n">
-        <v>7176654</v>
+        <v>7176769</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2587,6 +2582,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>vidväxt på högstubbe av gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2617,7 +2617,7 @@
         <v>123452603</v>
       </c>
       <c r="B19" t="n">
-        <v>57640</v>
+        <v>57643</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>

--- a/artfynd/A 9093-2025 artfynd.xlsx
+++ b/artfynd/A 9093-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>106170769</v>
       </c>
       <c r="B2" t="n">
-        <v>57490</v>
+        <v>57491</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1025,10 +1025,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123327865</v>
+        <v>123328272</v>
       </c>
       <c r="B5" t="n">
-        <v>57506</v>
+        <v>57507</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1073,10 +1073,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>800466</v>
+        <v>800517</v>
       </c>
       <c r="R5" t="n">
-        <v>7176708</v>
+        <v>7176634</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1113,7 +1113,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>hålhack i talltorraka</t>
+          <t>hack i gammal torraka</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1140,10 +1140,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123328272</v>
+        <v>123327865</v>
       </c>
       <c r="B6" t="n">
-        <v>57506</v>
+        <v>57507</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1188,10 +1188,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>800517</v>
+        <v>800466</v>
       </c>
       <c r="R6" t="n">
-        <v>7176634</v>
+        <v>7176708</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1228,7 +1228,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>hack i gammal torraka</t>
+          <t>hålhack i talltorraka</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1258,7 +1258,7 @@
         <v>123327889</v>
       </c>
       <c r="B7" t="n">
-        <v>78818</v>
+        <v>78820</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1368,7 +1368,7 @@
         <v>123327996</v>
       </c>
       <c r="B8" t="n">
-        <v>90988</v>
+        <v>90990</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>123327937</v>
       </c>
       <c r="B9" t="n">
-        <v>57506</v>
+        <v>57507</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123441000</v>
+        <v>123441144</v>
       </c>
       <c r="B10" t="n">
-        <v>57506</v>
+        <v>5176</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1602,33 +1602,34 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1638,10 +1639,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>800417</v>
+        <v>800585</v>
       </c>
       <c r="R10" t="n">
-        <v>7176768</v>
+        <v>7176730</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1678,7 +1679,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>hack i torraka</t>
+          <t>breda gnagspår i död gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1687,6 +1688,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1705,10 +1707,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123441111</v>
+        <v>123441387</v>
       </c>
       <c r="B11" t="n">
-        <v>78786</v>
+        <v>57491</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1721,30 +1723,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1752,10 +1755,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>800589</v>
+        <v>800647</v>
       </c>
       <c r="R11" t="n">
-        <v>7176762</v>
+        <v>7176653</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1790,13 +1793,17 @@
           <t>2025-03-21</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1815,10 +1822,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123441457</v>
+        <v>123441364</v>
       </c>
       <c r="B12" t="n">
-        <v>5176</v>
+        <v>90955</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1831,32 +1838,30 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100526</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1864,10 +1869,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>800660</v>
+        <v>800644</v>
       </c>
       <c r="R12" t="n">
-        <v>7176636</v>
+        <v>7176654</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1900,11 +1905,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>breda gångar i granlåga</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1935,7 +1935,7 @@
         <v>123441175</v>
       </c>
       <c r="B13" t="n">
-        <v>91006</v>
+        <v>91008</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2042,10 +2042,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123441038</v>
+        <v>123441000</v>
       </c>
       <c r="B14" t="n">
-        <v>57506</v>
+        <v>57507</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2090,10 +2090,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>800415</v>
+        <v>800417</v>
       </c>
       <c r="R14" t="n">
-        <v>7176760</v>
+        <v>7176768</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2130,7 +2130,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>hack i död gran</t>
+          <t>hack i torraka</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2157,10 +2157,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123441364</v>
+        <v>123441038</v>
       </c>
       <c r="B15" t="n">
-        <v>90953</v>
+        <v>57507</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2169,34 +2169,35 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2204,10 +2205,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>800644</v>
+        <v>800415</v>
       </c>
       <c r="R15" t="n">
-        <v>7176654</v>
+        <v>7176760</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2242,13 +2243,17 @@
           <t>2025-03-21</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>hack i död gran</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2267,10 +2272,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123441387</v>
+        <v>123441457</v>
       </c>
       <c r="B16" t="n">
-        <v>57490</v>
+        <v>5176</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2279,33 +2284,34 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>100526</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2315,10 +2321,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>800647</v>
+        <v>800660</v>
       </c>
       <c r="R16" t="n">
-        <v>7176653</v>
+        <v>7176636</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2355,7 +2361,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>barksprätt på gran</t>
+          <t>breda gångar i granlåga</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2364,6 +2370,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2382,10 +2389,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123441144</v>
+        <v>123441081</v>
       </c>
       <c r="B17" t="n">
-        <v>5176</v>
+        <v>90990</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2394,36 +2401,34 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2431,10 +2436,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>800585</v>
+        <v>800526</v>
       </c>
       <c r="R17" t="n">
-        <v>7176730</v>
+        <v>7176769</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2471,7 +2476,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>breda gnagspår i död gran</t>
+          <t>vidväxt på högstubbe av gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2499,10 +2504,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123441081</v>
+        <v>123441111</v>
       </c>
       <c r="B18" t="n">
-        <v>90988</v>
+        <v>78788</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2515,27 +2520,27 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -2546,10 +2551,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>800526</v>
+        <v>800589</v>
       </c>
       <c r="R18" t="n">
-        <v>7176769</v>
+        <v>7176762</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2582,11 +2587,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>vidväxt på högstubbe av gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2617,7 +2617,7 @@
         <v>123452603</v>
       </c>
       <c r="B19" t="n">
-        <v>57643</v>
+        <v>57644</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>

--- a/artfynd/A 9093-2025 artfynd.xlsx
+++ b/artfynd/A 9093-2025 artfynd.xlsx
@@ -1025,10 +1025,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123328272</v>
+        <v>123327889</v>
       </c>
       <c r="B5" t="n">
-        <v>57507</v>
+        <v>78820</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1041,31 +1041,30 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>185</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1073,10 +1072,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>800517</v>
+        <v>800568</v>
       </c>
       <c r="R5" t="n">
-        <v>7176634</v>
+        <v>7176666</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1111,17 +1110,13 @@
           <t>2025-03-14</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>hack i gammal torraka</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1140,10 +1135,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123327865</v>
+        <v>123327996</v>
       </c>
       <c r="B6" t="n">
-        <v>57507</v>
+        <v>90990</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1156,31 +1151,30 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1188,10 +1182,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>800466</v>
+        <v>800530</v>
       </c>
       <c r="R6" t="n">
-        <v>7176708</v>
+        <v>7176618</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1226,17 +1220,13 @@
           <t>2025-03-14</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>hålhack i talltorraka</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1255,10 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123327889</v>
+        <v>123327937</v>
       </c>
       <c r="B7" t="n">
-        <v>78820</v>
+        <v>57507</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1271,30 +1261,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>185</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1302,10 +1293,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>800568</v>
+        <v>800548</v>
       </c>
       <c r="R7" t="n">
-        <v>7176666</v>
+        <v>7176632</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1340,13 +1331,17 @@
           <t>2025-03-14</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>hack i gammal låga</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1365,10 +1360,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123327996</v>
+        <v>123327865</v>
       </c>
       <c r="B8" t="n">
-        <v>90990</v>
+        <v>57507</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1381,30 +1376,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1412,10 +1408,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>800530</v>
+        <v>800466</v>
       </c>
       <c r="R8" t="n">
-        <v>7176618</v>
+        <v>7176708</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1450,13 +1446,17 @@
           <t>2025-03-14</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>hålhack i talltorraka</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1475,7 +1475,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123327937</v>
+        <v>123328272</v>
       </c>
       <c r="B9" t="n">
         <v>57507</v>
@@ -1523,10 +1523,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>800548</v>
+        <v>800517</v>
       </c>
       <c r="R9" t="n">
-        <v>7176632</v>
+        <v>7176634</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>hack i gammal låga</t>
+          <t>hack i gammal torraka</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1590,7 +1590,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123441144</v>
+        <v>123441457</v>
       </c>
       <c r="B10" t="n">
         <v>5176</v>
@@ -1629,7 +1629,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>800585</v>
+        <v>800660</v>
       </c>
       <c r="R10" t="n">
-        <v>7176730</v>
+        <v>7176636</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>breda gnagspår i död gran</t>
+          <t>breda gångar i granlåga</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1707,10 +1707,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123441387</v>
+        <v>123441000</v>
       </c>
       <c r="B11" t="n">
-        <v>57491</v>
+        <v>57507</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1723,16 +1723,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1745,7 +1745,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1755,10 +1755,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>800647</v>
+        <v>800417</v>
       </c>
       <c r="R11" t="n">
-        <v>7176653</v>
+        <v>7176768</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1795,7 +1795,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>barksprätt på gran</t>
+          <t>hack i torraka</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1822,10 +1822,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123441364</v>
+        <v>123441387</v>
       </c>
       <c r="B12" t="n">
-        <v>90955</v>
+        <v>57491</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1834,34 +1834,35 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1869,10 +1870,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>800644</v>
+        <v>800647</v>
       </c>
       <c r="R12" t="n">
-        <v>7176654</v>
+        <v>7176653</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1907,13 +1908,17 @@
           <t>2025-03-21</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1932,10 +1937,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123441175</v>
+        <v>123441111</v>
       </c>
       <c r="B13" t="n">
-        <v>91008</v>
+        <v>78788</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1948,27 +1953,27 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1979,10 +1984,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>800571</v>
+        <v>800589</v>
       </c>
       <c r="R13" t="n">
-        <v>7176723</v>
+        <v>7176762</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2042,10 +2047,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123441000</v>
+        <v>123441364</v>
       </c>
       <c r="B14" t="n">
-        <v>57507</v>
+        <v>90955</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2054,35 +2059,34 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2090,10 +2094,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>800417</v>
+        <v>800644</v>
       </c>
       <c r="R14" t="n">
-        <v>7176768</v>
+        <v>7176654</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2128,17 +2132,13 @@
           <t>2025-03-21</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>hack i torraka</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2157,10 +2157,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123441038</v>
+        <v>123441144</v>
       </c>
       <c r="B15" t="n">
-        <v>57507</v>
+        <v>5176</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2169,33 +2169,34 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2205,10 +2206,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>800415</v>
+        <v>800585</v>
       </c>
       <c r="R15" t="n">
-        <v>7176760</v>
+        <v>7176730</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2245,7 +2246,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>hack i död gran</t>
+          <t>breda gnagspår i död gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2254,6 +2255,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2272,10 +2274,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123441457</v>
+        <v>123441038</v>
       </c>
       <c r="B16" t="n">
-        <v>5176</v>
+        <v>57507</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2284,34 +2286,33 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2321,10 +2322,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>800660</v>
+        <v>800415</v>
       </c>
       <c r="R16" t="n">
-        <v>7176636</v>
+        <v>7176760</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2361,7 +2362,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>breda gångar i granlåga</t>
+          <t>hack i död gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2370,7 +2371,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2389,10 +2389,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123441081</v>
+        <v>123441175</v>
       </c>
       <c r="B17" t="n">
-        <v>90990</v>
+        <v>91008</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2405,21 +2405,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2436,10 +2436,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>800526</v>
+        <v>800571</v>
       </c>
       <c r="R17" t="n">
-        <v>7176769</v>
+        <v>7176723</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2472,11 +2472,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>vidväxt på högstubbe av gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2504,10 +2499,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123441111</v>
+        <v>123441081</v>
       </c>
       <c r="B18" t="n">
-        <v>78788</v>
+        <v>90990</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2520,27 +2515,27 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -2551,10 +2546,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>800589</v>
+        <v>800526</v>
       </c>
       <c r="R18" t="n">
-        <v>7176762</v>
+        <v>7176769</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2587,6 +2582,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>vidväxt på högstubbe av gran</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 9093-2025 artfynd.xlsx
+++ b/artfynd/A 9093-2025 artfynd.xlsx
@@ -1707,10 +1707,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123441000</v>
+        <v>123441387</v>
       </c>
       <c r="B11" t="n">
-        <v>57507</v>
+        <v>57491</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1723,16 +1723,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1745,7 +1745,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1755,10 +1755,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>800417</v>
+        <v>800647</v>
       </c>
       <c r="R11" t="n">
-        <v>7176768</v>
+        <v>7176653</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1795,7 +1795,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>hack i torraka</t>
+          <t>barksprätt på gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1822,10 +1822,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123441387</v>
+        <v>123441000</v>
       </c>
       <c r="B12" t="n">
-        <v>57491</v>
+        <v>57507</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1838,16 +1838,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1860,7 +1860,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1870,10 +1870,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>800647</v>
+        <v>800417</v>
       </c>
       <c r="R12" t="n">
-        <v>7176653</v>
+        <v>7176768</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1910,7 +1910,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>barksprätt på gran</t>
+          <t>hack i torraka</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 9093-2025 artfynd.xlsx
+++ b/artfynd/A 9093-2025 artfynd.xlsx
@@ -1135,10 +1135,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123327996</v>
+        <v>123327937</v>
       </c>
       <c r="B6" t="n">
-        <v>90990</v>
+        <v>57507</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1151,30 +1151,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1182,10 +1183,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>800530</v>
+        <v>800548</v>
       </c>
       <c r="R6" t="n">
-        <v>7176618</v>
+        <v>7176632</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1220,13 +1221,17 @@
           <t>2025-03-14</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>hack i gammal låga</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1245,7 +1250,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123327937</v>
+        <v>123327865</v>
       </c>
       <c r="B7" t="n">
         <v>57507</v>
@@ -1293,10 +1298,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>800548</v>
+        <v>800466</v>
       </c>
       <c r="R7" t="n">
-        <v>7176632</v>
+        <v>7176708</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1333,7 +1338,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>hack i gammal låga</t>
+          <t>hålhack i talltorraka</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1360,10 +1365,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123327865</v>
+        <v>123327996</v>
       </c>
       <c r="B8" t="n">
-        <v>57507</v>
+        <v>90990</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1376,31 +1381,30 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1408,10 +1412,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>800466</v>
+        <v>800530</v>
       </c>
       <c r="R8" t="n">
-        <v>7176708</v>
+        <v>7176618</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1446,17 +1450,13 @@
           <t>2025-03-14</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>hålhack i talltorraka</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1590,10 +1590,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123441457</v>
+        <v>123441081</v>
       </c>
       <c r="B10" t="n">
-        <v>5176</v>
+        <v>90990</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1602,36 +1602,34 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1639,10 +1637,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>800660</v>
+        <v>800526</v>
       </c>
       <c r="R10" t="n">
-        <v>7176636</v>
+        <v>7176769</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1679,7 +1677,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>breda gångar i granlåga</t>
+          <t>vidväxt på högstubbe av gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1707,10 +1705,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123441387</v>
+        <v>123441111</v>
       </c>
       <c r="B11" t="n">
-        <v>57491</v>
+        <v>78788</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1723,31 +1721,30 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1755,10 +1752,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>800647</v>
+        <v>800589</v>
       </c>
       <c r="R11" t="n">
-        <v>7176653</v>
+        <v>7176762</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1793,17 +1790,13 @@
           <t>2025-03-21</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>barksprätt på gran</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1822,10 +1815,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123441000</v>
+        <v>123441387</v>
       </c>
       <c r="B12" t="n">
-        <v>57507</v>
+        <v>57491</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1838,16 +1831,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1860,7 +1853,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1870,10 +1863,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>800417</v>
+        <v>800647</v>
       </c>
       <c r="R12" t="n">
-        <v>7176768</v>
+        <v>7176653</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1910,7 +1903,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>hack i torraka</t>
+          <t>barksprätt på gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1937,10 +1930,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123441111</v>
+        <v>123441038</v>
       </c>
       <c r="B13" t="n">
-        <v>78788</v>
+        <v>57507</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1953,30 +1946,31 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1984,10 +1978,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>800589</v>
+        <v>800415</v>
       </c>
       <c r="R13" t="n">
-        <v>7176762</v>
+        <v>7176760</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2022,13 +2016,17 @@
           <t>2025-03-21</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>hack i död gran</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2047,10 +2045,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123441364</v>
+        <v>123441175</v>
       </c>
       <c r="B14" t="n">
-        <v>90955</v>
+        <v>91008</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2059,25 +2057,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2094,10 +2092,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>800644</v>
+        <v>800571</v>
       </c>
       <c r="R14" t="n">
-        <v>7176654</v>
+        <v>7176723</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2157,10 +2155,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123441144</v>
+        <v>123441000</v>
       </c>
       <c r="B15" t="n">
-        <v>5176</v>
+        <v>57507</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2169,34 +2167,33 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2206,10 +2203,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>800585</v>
+        <v>800417</v>
       </c>
       <c r="R15" t="n">
-        <v>7176730</v>
+        <v>7176768</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2246,7 +2243,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>breda gnagspår i död gran</t>
+          <t>hack i torraka</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2255,7 +2252,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2274,10 +2270,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123441038</v>
+        <v>123441457</v>
       </c>
       <c r="B16" t="n">
-        <v>57507</v>
+        <v>5176</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2286,33 +2282,34 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2322,10 +2319,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>800415</v>
+        <v>800660</v>
       </c>
       <c r="R16" t="n">
-        <v>7176760</v>
+        <v>7176636</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2362,7 +2359,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>hack i död gran</t>
+          <t>breda gångar i granlåga</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2371,6 +2368,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2389,10 +2387,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123441175</v>
+        <v>123441364</v>
       </c>
       <c r="B17" t="n">
-        <v>91008</v>
+        <v>90955</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2401,25 +2399,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2436,10 +2434,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>800571</v>
+        <v>800644</v>
       </c>
       <c r="R17" t="n">
-        <v>7176723</v>
+        <v>7176654</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2499,10 +2497,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123441081</v>
+        <v>123441144</v>
       </c>
       <c r="B18" t="n">
-        <v>90990</v>
+        <v>5176</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2511,34 +2509,36 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2546,10 +2546,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>800526</v>
+        <v>800585</v>
       </c>
       <c r="R18" t="n">
-        <v>7176769</v>
+        <v>7176730</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2586,7 +2586,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>vidväxt på högstubbe av gran</t>
+          <t>breda gnagspår i död gran</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 9093-2025 artfynd.xlsx
+++ b/artfynd/A 9093-2025 artfynd.xlsx
@@ -1025,10 +1025,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123327889</v>
+        <v>123327865</v>
       </c>
       <c r="B5" t="n">
-        <v>78820</v>
+        <v>57507</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1041,30 +1041,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>185</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1072,10 +1073,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>800568</v>
+        <v>800466</v>
       </c>
       <c r="R5" t="n">
-        <v>7176666</v>
+        <v>7176708</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1110,13 +1111,17 @@
           <t>2025-03-14</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>hålhack i talltorraka</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1135,7 +1140,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123327937</v>
+        <v>123328272</v>
       </c>
       <c r="B6" t="n">
         <v>57507</v>
@@ -1183,10 +1188,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>800548</v>
+        <v>800517</v>
       </c>
       <c r="R6" t="n">
-        <v>7176632</v>
+        <v>7176634</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1223,7 +1228,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>hack i gammal låga</t>
+          <t>hack i gammal torraka</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1250,7 +1255,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123327865</v>
+        <v>123327937</v>
       </c>
       <c r="B7" t="n">
         <v>57507</v>
@@ -1298,10 +1303,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>800466</v>
+        <v>800548</v>
       </c>
       <c r="R7" t="n">
-        <v>7176708</v>
+        <v>7176632</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1338,7 +1343,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>hålhack i talltorraka</t>
+          <t>hack i gammal låga</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1475,10 +1480,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123328272</v>
+        <v>123327889</v>
       </c>
       <c r="B9" t="n">
-        <v>57507</v>
+        <v>78820</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1491,31 +1496,30 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>185</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1523,10 +1527,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>800517</v>
+        <v>800568</v>
       </c>
       <c r="R9" t="n">
-        <v>7176634</v>
+        <v>7176666</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1561,17 +1565,13 @@
           <t>2025-03-14</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>hack i gammal torraka</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1590,10 +1590,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123441081</v>
+        <v>123441387</v>
       </c>
       <c r="B10" t="n">
-        <v>90990</v>
+        <v>57491</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1606,30 +1606,31 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1637,10 +1638,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>800526</v>
+        <v>800647</v>
       </c>
       <c r="R10" t="n">
-        <v>7176769</v>
+        <v>7176653</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1677,7 +1678,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>vidväxt på högstubbe av gran</t>
+          <t>barksprätt på gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1686,7 +1687,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1705,10 +1705,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123441111</v>
+        <v>123441364</v>
       </c>
       <c r="B11" t="n">
-        <v>78788</v>
+        <v>90955</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1717,31 +1717,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1752,10 +1752,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>800589</v>
+        <v>800644</v>
       </c>
       <c r="R11" t="n">
-        <v>7176762</v>
+        <v>7176654</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1815,10 +1815,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123441387</v>
+        <v>123441175</v>
       </c>
       <c r="B12" t="n">
-        <v>57491</v>
+        <v>91008</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1831,31 +1831,30 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1863,10 +1862,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>800647</v>
+        <v>800571</v>
       </c>
       <c r="R12" t="n">
-        <v>7176653</v>
+        <v>7176723</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1901,17 +1900,13 @@
           <t>2025-03-21</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>barksprätt på gran</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1930,10 +1925,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123441038</v>
+        <v>123441081</v>
       </c>
       <c r="B13" t="n">
-        <v>57507</v>
+        <v>90990</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1946,31 +1941,30 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1978,10 +1972,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>800415</v>
+        <v>800526</v>
       </c>
       <c r="R13" t="n">
-        <v>7176760</v>
+        <v>7176769</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2018,7 +2012,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>hack i död gran</t>
+          <t>vidväxt på högstubbe av gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2027,6 +2021,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2045,10 +2040,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123441175</v>
+        <v>123441111</v>
       </c>
       <c r="B14" t="n">
-        <v>91008</v>
+        <v>78788</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2061,27 +2056,27 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -2092,10 +2087,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>800571</v>
+        <v>800589</v>
       </c>
       <c r="R14" t="n">
-        <v>7176723</v>
+        <v>7176762</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2155,7 +2150,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123441000</v>
+        <v>123441038</v>
       </c>
       <c r="B15" t="n">
         <v>57507</v>
@@ -2203,10 +2198,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>800417</v>
+        <v>800415</v>
       </c>
       <c r="R15" t="n">
-        <v>7176768</v>
+        <v>7176760</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2243,7 +2238,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>hack i torraka</t>
+          <t>hack i död gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2270,7 +2265,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123441457</v>
+        <v>123441144</v>
       </c>
       <c r="B16" t="n">
         <v>5176</v>
@@ -2309,7 +2304,7 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2319,10 +2314,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>800660</v>
+        <v>800585</v>
       </c>
       <c r="R16" t="n">
-        <v>7176636</v>
+        <v>7176730</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2359,7 +2354,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>breda gångar i granlåga</t>
+          <t>breda gnagspår i död gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2387,10 +2382,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123441364</v>
+        <v>123441000</v>
       </c>
       <c r="B17" t="n">
-        <v>90955</v>
+        <v>57507</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2399,34 +2394,35 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2434,10 +2430,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>800644</v>
+        <v>800417</v>
       </c>
       <c r="R17" t="n">
-        <v>7176654</v>
+        <v>7176768</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2472,13 +2468,17 @@
           <t>2025-03-21</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>hack i torraka</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2497,7 +2497,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123441144</v>
+        <v>123441457</v>
       </c>
       <c r="B18" t="n">
         <v>5176</v>
@@ -2536,7 +2536,7 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2546,10 +2546,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>800585</v>
+        <v>800660</v>
       </c>
       <c r="R18" t="n">
-        <v>7176730</v>
+        <v>7176636</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2586,7 +2586,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>breda gnagspår i död gran</t>
+          <t>breda gångar i granlåga</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 9093-2025 artfynd.xlsx
+++ b/artfynd/A 9093-2025 artfynd.xlsx
@@ -1255,10 +1255,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123327937</v>
+        <v>123327889</v>
       </c>
       <c r="B7" t="n">
-        <v>57507</v>
+        <v>78820</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1271,31 +1271,30 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>185</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1303,10 +1302,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>800548</v>
+        <v>800568</v>
       </c>
       <c r="R7" t="n">
-        <v>7176632</v>
+        <v>7176666</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1341,17 +1340,13 @@
           <t>2025-03-14</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>hack i gammal låga</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1480,10 +1475,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123327889</v>
+        <v>123327937</v>
       </c>
       <c r="B9" t="n">
-        <v>78820</v>
+        <v>57507</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1496,30 +1491,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>185</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1527,10 +1523,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>800568</v>
+        <v>800548</v>
       </c>
       <c r="R9" t="n">
-        <v>7176666</v>
+        <v>7176632</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1565,13 +1561,17 @@
           <t>2025-03-14</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>hack i gammal låga</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1590,10 +1590,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123441387</v>
+        <v>123441457</v>
       </c>
       <c r="B10" t="n">
-        <v>57491</v>
+        <v>5176</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1602,33 +1602,34 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>100526</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1638,10 +1639,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>800647</v>
+        <v>800660</v>
       </c>
       <c r="R10" t="n">
-        <v>7176653</v>
+        <v>7176636</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1678,7 +1679,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>barksprätt på gran</t>
+          <t>breda gångar i granlåga</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1687,6 +1688,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1705,10 +1707,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123441364</v>
+        <v>123441144</v>
       </c>
       <c r="B11" t="n">
-        <v>90955</v>
+        <v>5176</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1721,30 +1723,32 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>100526</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1752,10 +1756,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>800644</v>
+        <v>800585</v>
       </c>
       <c r="R11" t="n">
-        <v>7176654</v>
+        <v>7176730</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1788,6 +1792,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>breda gnagspår i död gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1815,10 +1824,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123441175</v>
+        <v>123441111</v>
       </c>
       <c r="B12" t="n">
-        <v>91008</v>
+        <v>78788</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1831,27 +1840,27 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1862,10 +1871,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>800571</v>
+        <v>800589</v>
       </c>
       <c r="R12" t="n">
-        <v>7176723</v>
+        <v>7176762</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1925,10 +1934,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123441081</v>
+        <v>123441000</v>
       </c>
       <c r="B13" t="n">
-        <v>90990</v>
+        <v>57507</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1941,30 +1950,31 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1972,10 +1982,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>800526</v>
+        <v>800417</v>
       </c>
       <c r="R13" t="n">
-        <v>7176769</v>
+        <v>7176768</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2012,7 +2022,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>vidväxt på högstubbe av gran</t>
+          <t>hack i torraka</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2021,7 +2031,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2040,10 +2049,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123441111</v>
+        <v>123441387</v>
       </c>
       <c r="B14" t="n">
-        <v>78788</v>
+        <v>57491</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2056,30 +2065,31 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2087,10 +2097,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>800589</v>
+        <v>800647</v>
       </c>
       <c r="R14" t="n">
-        <v>7176762</v>
+        <v>7176653</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2125,13 +2135,17 @@
           <t>2025-03-21</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2150,10 +2164,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123441038</v>
+        <v>123441175</v>
       </c>
       <c r="B15" t="n">
-        <v>57507</v>
+        <v>91008</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2166,31 +2180,30 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2198,10 +2211,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>800415</v>
+        <v>800571</v>
       </c>
       <c r="R15" t="n">
-        <v>7176760</v>
+        <v>7176723</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2236,17 +2249,13 @@
           <t>2025-03-21</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>hack i död gran</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2265,10 +2274,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123441144</v>
+        <v>123441038</v>
       </c>
       <c r="B16" t="n">
-        <v>5176</v>
+        <v>57507</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2277,34 +2286,33 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2314,10 +2322,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>800585</v>
+        <v>800415</v>
       </c>
       <c r="R16" t="n">
-        <v>7176730</v>
+        <v>7176760</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2354,7 +2362,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>breda gnagspår i död gran</t>
+          <t>hack i död gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2363,7 +2371,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2382,10 +2389,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123441000</v>
+        <v>123441081</v>
       </c>
       <c r="B17" t="n">
-        <v>57507</v>
+        <v>90990</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2398,31 +2405,30 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2430,10 +2436,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>800417</v>
+        <v>800526</v>
       </c>
       <c r="R17" t="n">
-        <v>7176768</v>
+        <v>7176769</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2470,7 +2476,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>hack i torraka</t>
+          <t>vidväxt på högstubbe av gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2479,6 +2485,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2497,10 +2504,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123441457</v>
+        <v>123441364</v>
       </c>
       <c r="B18" t="n">
-        <v>5176</v>
+        <v>90955</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2513,32 +2520,30 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100526</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2546,10 +2551,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>800660</v>
+        <v>800644</v>
       </c>
       <c r="R18" t="n">
-        <v>7176636</v>
+        <v>7176654</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2582,11 +2587,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>breda gångar i granlåga</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 9093-2025 artfynd.xlsx
+++ b/artfynd/A 9093-2025 artfynd.xlsx
@@ -1025,7 +1025,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123327865</v>
+        <v>123328272</v>
       </c>
       <c r="B5" t="n">
         <v>57507</v>
@@ -1073,10 +1073,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>800466</v>
+        <v>800517</v>
       </c>
       <c r="R5" t="n">
-        <v>7176708</v>
+        <v>7176634</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1113,7 +1113,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>hålhack i talltorraka</t>
+          <t>hack i gammal torraka</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1140,10 +1140,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123328272</v>
+        <v>123327996</v>
       </c>
       <c r="B6" t="n">
-        <v>57507</v>
+        <v>90990</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1156,31 +1156,30 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1188,10 +1187,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>800517</v>
+        <v>800530</v>
       </c>
       <c r="R6" t="n">
-        <v>7176634</v>
+        <v>7176618</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1226,17 +1225,13 @@
           <t>2025-03-14</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>hack i gammal torraka</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1255,10 +1250,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123327889</v>
+        <v>123327937</v>
       </c>
       <c r="B7" t="n">
-        <v>78820</v>
+        <v>57507</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1271,30 +1266,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>185</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1302,10 +1298,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>800568</v>
+        <v>800548</v>
       </c>
       <c r="R7" t="n">
-        <v>7176666</v>
+        <v>7176632</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1340,13 +1336,17 @@
           <t>2025-03-14</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>hack i gammal låga</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1365,10 +1365,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123327996</v>
+        <v>123327889</v>
       </c>
       <c r="B8" t="n">
-        <v>90990</v>
+        <v>78820</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1381,27 +1381,27 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>185</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -1412,10 +1412,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>800530</v>
+        <v>800568</v>
       </c>
       <c r="R8" t="n">
-        <v>7176618</v>
+        <v>7176666</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1475,7 +1475,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123327937</v>
+        <v>123327865</v>
       </c>
       <c r="B9" t="n">
         <v>57507</v>
@@ -1523,10 +1523,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>800548</v>
+        <v>800466</v>
       </c>
       <c r="R9" t="n">
-        <v>7176632</v>
+        <v>7176708</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>hack i gammal låga</t>
+          <t>hålhack i talltorraka</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1590,10 +1590,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123441457</v>
+        <v>123441111</v>
       </c>
       <c r="B10" t="n">
-        <v>5176</v>
+        <v>78788</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1602,36 +1602,34 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1639,10 +1637,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>800660</v>
+        <v>800589</v>
       </c>
       <c r="R10" t="n">
-        <v>7176636</v>
+        <v>7176762</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1675,11 +1673,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>breda gångar i granlåga</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1707,10 +1700,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123441144</v>
+        <v>123441038</v>
       </c>
       <c r="B11" t="n">
-        <v>5176</v>
+        <v>57507</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1719,34 +1712,33 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1756,10 +1748,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>800585</v>
+        <v>800415</v>
       </c>
       <c r="R11" t="n">
-        <v>7176730</v>
+        <v>7176760</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1796,7 +1788,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>breda gnagspår i död gran</t>
+          <t>hack i död gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1805,7 +1797,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1824,10 +1815,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123441111</v>
+        <v>123441144</v>
       </c>
       <c r="B12" t="n">
-        <v>78788</v>
+        <v>5176</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1836,34 +1827,36 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1871,10 +1864,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>800589</v>
+        <v>800585</v>
       </c>
       <c r="R12" t="n">
-        <v>7176762</v>
+        <v>7176730</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1907,6 +1900,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>breda gnagspår i död gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2049,10 +2047,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123441387</v>
+        <v>123441175</v>
       </c>
       <c r="B14" t="n">
-        <v>57491</v>
+        <v>91008</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2065,31 +2063,30 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2097,10 +2094,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>800647</v>
+        <v>800571</v>
       </c>
       <c r="R14" t="n">
-        <v>7176653</v>
+        <v>7176723</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2135,17 +2132,13 @@
           <t>2025-03-21</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>barksprätt på gran</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2164,10 +2157,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123441175</v>
+        <v>123441364</v>
       </c>
       <c r="B15" t="n">
-        <v>91008</v>
+        <v>90955</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2176,25 +2169,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2211,10 +2204,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>800571</v>
+        <v>800644</v>
       </c>
       <c r="R15" t="n">
-        <v>7176723</v>
+        <v>7176654</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2274,10 +2267,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123441038</v>
+        <v>123441081</v>
       </c>
       <c r="B16" t="n">
-        <v>57507</v>
+        <v>90990</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2290,31 +2283,30 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2322,10 +2314,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>800415</v>
+        <v>800526</v>
       </c>
       <c r="R16" t="n">
-        <v>7176760</v>
+        <v>7176769</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2362,7 +2354,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>hack i död gran</t>
+          <t>vidväxt på högstubbe av gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2371,6 +2363,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2389,10 +2382,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123441081</v>
+        <v>123441387</v>
       </c>
       <c r="B17" t="n">
-        <v>90990</v>
+        <v>57491</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2405,30 +2398,31 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2436,10 +2430,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>800526</v>
+        <v>800647</v>
       </c>
       <c r="R17" t="n">
-        <v>7176769</v>
+        <v>7176653</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2476,7 +2470,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>vidväxt på högstubbe av gran</t>
+          <t>barksprätt på gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2485,7 +2479,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2504,10 +2497,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123441364</v>
+        <v>123441457</v>
       </c>
       <c r="B18" t="n">
-        <v>90955</v>
+        <v>5176</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2520,30 +2513,32 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>100526</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2551,10 +2546,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>800644</v>
+        <v>800660</v>
       </c>
       <c r="R18" t="n">
-        <v>7176654</v>
+        <v>7176636</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2587,6 +2582,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>breda gångar i granlåga</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 9093-2025 artfynd.xlsx
+++ b/artfynd/A 9093-2025 artfynd.xlsx
@@ -1593,7 +1593,7 @@
         <v>123441387</v>
       </c>
       <c r="B10" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 9093-2025 artfynd.xlsx
+++ b/artfynd/A 9093-2025 artfynd.xlsx
@@ -1595,11 +1595,6 @@
       <c r="B10" t="n">
         <v>57635</v>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D10" t="inlineStr">
         <is>
           <t>NT</t>

--- a/artfynd/A 9093-2025 artfynd.xlsx
+++ b/artfynd/A 9093-2025 artfynd.xlsx
@@ -2727,7 +2727,7 @@
         <v>127101303</v>
       </c>
       <c r="B20" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Patrik Nygren, Sirirat Chanon</t>
+          <t>Sirirat Chanon, Patrik Nygren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2829,7 +2829,7 @@
         <v>127101711</v>
       </c>
       <c r="B21" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
         <v>127101557</v>
       </c>
       <c r="B22" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
         <v>127101796</v>
       </c>
       <c r="B23" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3136,10 +3136,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127087398</v>
+        <v>127101010</v>
       </c>
       <c r="B24" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3171,14 +3171,14 @@
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Södra Bergfors, Vb</t>
+          <t>Södra Bergfors , Vb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>800541</v>
+        <v>800532</v>
       </c>
       <c r="R24" t="n">
-        <v>7176644</v>
+        <v>7176632</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3231,17 +3231,17 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Patrik Nygren, Sirirat Chanon</t>
+          <t>Sirirat Chanon, Patrik Nygren</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127101010</v>
+        <v>127087398</v>
       </c>
       <c r="B25" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3273,14 +3273,14 @@
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Södra Bergfors , Vb</t>
+          <t>Södra Bergfors, Vb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>800532</v>
+        <v>800541</v>
       </c>
       <c r="R25" t="n">
-        <v>7176632</v>
+        <v>7176644</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>

--- a/artfynd/A 9093-2025 artfynd.xlsx
+++ b/artfynd/A 9093-2025 artfynd.xlsx
@@ -2727,7 +2727,7 @@
         <v>127101303</v>
       </c>
       <c r="B20" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2829,7 +2829,7 @@
         <v>127101711</v>
       </c>
       <c r="B21" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
         <v>127101557</v>
       </c>
       <c r="B22" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
         <v>127101796</v>
       </c>
       <c r="B23" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3136,10 +3136,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127101010</v>
+        <v>127087398</v>
       </c>
       <c r="B24" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3171,14 +3171,14 @@
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Södra Bergfors , Vb</t>
+          <t>Södra Bergfors, Vb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>800532</v>
+        <v>800541</v>
       </c>
       <c r="R24" t="n">
-        <v>7176632</v>
+        <v>7176644</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3231,17 +3231,17 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Sirirat Chanon, Patrik Nygren</t>
+          <t>Patrik Nygren, Sirirat Chanon</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127087398</v>
+        <v>127101010</v>
       </c>
       <c r="B25" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3273,14 +3273,14 @@
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Södra Bergfors, Vb</t>
+          <t>Södra Bergfors , Vb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>800541</v>
+        <v>800532</v>
       </c>
       <c r="R25" t="n">
-        <v>7176644</v>
+        <v>7176632</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>

--- a/artfynd/A 9093-2025 artfynd.xlsx
+++ b/artfynd/A 9093-2025 artfynd.xlsx
@@ -3136,7 +3136,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127087398</v>
+        <v>127101010</v>
       </c>
       <c r="B24" t="n">
         <v>98442</v>
@@ -3171,14 +3171,14 @@
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Södra Bergfors, Vb</t>
+          <t>Södra Bergfors , Vb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>800541</v>
+        <v>800532</v>
       </c>
       <c r="R24" t="n">
-        <v>7176644</v>
+        <v>7176632</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3238,7 +3238,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127101010</v>
+        <v>127087398</v>
       </c>
       <c r="B25" t="n">
         <v>98442</v>
@@ -3273,14 +3273,14 @@
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Södra Bergfors , Vb</t>
+          <t>Södra Bergfors, Vb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>800532</v>
+        <v>800541</v>
       </c>
       <c r="R25" t="n">
-        <v>7176632</v>
+        <v>7176644</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>

--- a/artfynd/A 9093-2025 artfynd.xlsx
+++ b/artfynd/A 9093-2025 artfynd.xlsx
@@ -2727,7 +2727,7 @@
         <v>127101303</v>
       </c>
       <c r="B20" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Sirirat Chanon, Patrik Nygren</t>
+          <t>Patrik Nygren, Sirirat Chanon</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2829,7 +2829,7 @@
         <v>127101711</v>
       </c>
       <c r="B21" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
         <v>127101557</v>
       </c>
       <c r="B22" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
         <v>127101796</v>
       </c>
       <c r="B23" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3139,7 +3139,7 @@
         <v>127101010</v>
       </c>
       <c r="B24" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3241,7 +3241,7 @@
         <v>127087398</v>
       </c>
       <c r="B25" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 9093-2025 artfynd.xlsx
+++ b/artfynd/A 9093-2025 artfynd.xlsx
@@ -2819,7 +2819,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Patrik Nygren, Sirirat Chanon</t>
+          <t>Sirirat Chanon, Patrik Nygren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>

--- a/artfynd/A 9093-2025 artfynd.xlsx
+++ b/artfynd/A 9093-2025 artfynd.xlsx
@@ -2727,7 +2727,7 @@
         <v>127101303</v>
       </c>
       <c r="B20" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2829,7 +2829,7 @@
         <v>127101711</v>
       </c>
       <c r="B21" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
         <v>127101557</v>
       </c>
       <c r="B22" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
         <v>127101796</v>
       </c>
       <c r="B23" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3139,7 +3139,7 @@
         <v>127101010</v>
       </c>
       <c r="B24" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3241,7 +3241,7 @@
         <v>127087398</v>
       </c>
       <c r="B25" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 9093-2025 artfynd.xlsx
+++ b/artfynd/A 9093-2025 artfynd.xlsx
@@ -2727,7 +2727,7 @@
         <v>127101303</v>
       </c>
       <c r="B20" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2829,7 +2829,7 @@
         <v>127101711</v>
       </c>
       <c r="B21" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
         <v>127101557</v>
       </c>
       <c r="B22" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
         <v>127101796</v>
       </c>
       <c r="B23" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3129,17 +3129,17 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Patrik Nygren, Sirirat Chanon</t>
+          <t>Sirirat Chanon, Patrik Nygren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127101010</v>
+        <v>127087398</v>
       </c>
       <c r="B24" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3171,14 +3171,14 @@
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Södra Bergfors , Vb</t>
+          <t>Södra Bergfors, Vb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>800532</v>
+        <v>800541</v>
       </c>
       <c r="R24" t="n">
-        <v>7176632</v>
+        <v>7176644</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3238,10 +3238,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127087398</v>
+        <v>127101010</v>
       </c>
       <c r="B25" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3273,14 +3273,14 @@
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Södra Bergfors, Vb</t>
+          <t>Södra Bergfors , Vb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>800541</v>
+        <v>800532</v>
       </c>
       <c r="R25" t="n">
-        <v>7176644</v>
+        <v>7176632</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>

--- a/artfynd/A 9093-2025 artfynd.xlsx
+++ b/artfynd/A 9093-2025 artfynd.xlsx
@@ -2727,7 +2727,7 @@
         <v>127101303</v>
       </c>
       <c r="B20" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2826,10 +2826,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127101711</v>
+        <v>127101557</v>
       </c>
       <c r="B21" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2856,7 +2856,11 @@
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
@@ -2865,10 +2869,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>800648</v>
+        <v>800518</v>
       </c>
       <c r="R21" t="n">
-        <v>7176649</v>
+        <v>7176638</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2928,10 +2932,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127101557</v>
+        <v>127101711</v>
       </c>
       <c r="B22" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2958,11 +2962,7 @@
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
@@ -2971,10 +2971,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>800518</v>
+        <v>800648</v>
       </c>
       <c r="R22" t="n">
-        <v>7176638</v>
+        <v>7176649</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3037,7 +3037,7 @@
         <v>127101796</v>
       </c>
       <c r="B23" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3129,17 +3129,17 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Sirirat Chanon, Patrik Nygren</t>
+          <t>Patrik Nygren, Sirirat Chanon</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127087398</v>
+        <v>127101010</v>
       </c>
       <c r="B24" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3171,14 +3171,14 @@
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Södra Bergfors, Vb</t>
+          <t>Södra Bergfors , Vb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>800541</v>
+        <v>800532</v>
       </c>
       <c r="R24" t="n">
-        <v>7176644</v>
+        <v>7176632</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3238,10 +3238,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127101010</v>
+        <v>127087398</v>
       </c>
       <c r="B25" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3273,14 +3273,14 @@
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Södra Bergfors , Vb</t>
+          <t>Södra Bergfors, Vb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>800532</v>
+        <v>800541</v>
       </c>
       <c r="R25" t="n">
-        <v>7176632</v>
+        <v>7176644</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>

--- a/artfynd/A 9093-2025 artfynd.xlsx
+++ b/artfynd/A 9093-2025 artfynd.xlsx
@@ -2826,7 +2826,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127101557</v>
+        <v>127101711</v>
       </c>
       <c r="B21" t="n">
         <v>98450</v>
@@ -2856,11 +2856,7 @@
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
@@ -2869,10 +2865,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>800518</v>
+        <v>800648</v>
       </c>
       <c r="R21" t="n">
-        <v>7176638</v>
+        <v>7176649</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2932,7 +2928,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127101711</v>
+        <v>127101557</v>
       </c>
       <c r="B22" t="n">
         <v>98450</v>
@@ -2962,7 +2958,11 @@
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
@@ -2971,10 +2971,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>800648</v>
+        <v>800518</v>
       </c>
       <c r="R22" t="n">
-        <v>7176649</v>
+        <v>7176638</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3129,14 +3129,14 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Patrik Nygren, Sirirat Chanon</t>
+          <t>Sirirat Chanon, Patrik Nygren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127101010</v>
+        <v>127087398</v>
       </c>
       <c r="B24" t="n">
         <v>98450</v>
@@ -3171,14 +3171,14 @@
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Södra Bergfors , Vb</t>
+          <t>Södra Bergfors, Vb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>800532</v>
+        <v>800541</v>
       </c>
       <c r="R24" t="n">
-        <v>7176632</v>
+        <v>7176644</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3238,7 +3238,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127087398</v>
+        <v>127101010</v>
       </c>
       <c r="B25" t="n">
         <v>98450</v>
@@ -3273,14 +3273,14 @@
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Södra Bergfors, Vb</t>
+          <t>Södra Bergfors , Vb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>800541</v>
+        <v>800532</v>
       </c>
       <c r="R25" t="n">
-        <v>7176644</v>
+        <v>7176632</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>

--- a/artfynd/A 9093-2025 artfynd.xlsx
+++ b/artfynd/A 9093-2025 artfynd.xlsx
@@ -3129,7 +3129,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Sirirat Chanon, Patrik Nygren</t>
+          <t>Patrik Nygren, Sirirat Chanon</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>

--- a/artfynd/A 9093-2025 artfynd.xlsx
+++ b/artfynd/A 9093-2025 artfynd.xlsx
@@ -2727,7 +2727,7 @@
         <v>127101303</v>
       </c>
       <c r="B20" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2829,7 +2829,7 @@
         <v>127101711</v>
       </c>
       <c r="B21" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
         <v>127101557</v>
       </c>
       <c r="B22" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
         <v>127101796</v>
       </c>
       <c r="B23" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3139,7 +3139,7 @@
         <v>127087398</v>
       </c>
       <c r="B24" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3241,7 +3241,7 @@
         <v>127101010</v>
       </c>
       <c r="B25" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 9093-2025 artfynd.xlsx
+++ b/artfynd/A 9093-2025 artfynd.xlsx
@@ -2727,7 +2727,7 @@
         <v>127101303</v>
       </c>
       <c r="B20" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Sirirat Chanon, Patrik Nygren</t>
+          <t>Patrik Nygren, Sirirat Chanon</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2829,7 +2829,7 @@
         <v>127101711</v>
       </c>
       <c r="B21" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
         <v>127101557</v>
       </c>
       <c r="B22" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
         <v>127101796</v>
       </c>
       <c r="B23" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3136,10 +3136,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127087398</v>
+        <v>127101010</v>
       </c>
       <c r="B24" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3171,14 +3171,14 @@
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Södra Bergfors, Vb</t>
+          <t>Södra Bergfors , Vb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>800541</v>
+        <v>800532</v>
       </c>
       <c r="R24" t="n">
-        <v>7176644</v>
+        <v>7176632</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3238,10 +3238,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127101010</v>
+        <v>127087398</v>
       </c>
       <c r="B25" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3273,14 +3273,14 @@
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Södra Bergfors , Vb</t>
+          <t>Södra Bergfors, Vb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>800532</v>
+        <v>800541</v>
       </c>
       <c r="R25" t="n">
-        <v>7176632</v>
+        <v>7176644</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>

--- a/artfynd/A 9093-2025 artfynd.xlsx
+++ b/artfynd/A 9093-2025 artfynd.xlsx
@@ -2727,7 +2727,7 @@
         <v>127101303</v>
       </c>
       <c r="B20" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Patrik Nygren, Sirirat Chanon</t>
+          <t>Sirirat Chanon, Patrik Nygren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2829,7 +2829,7 @@
         <v>127101711</v>
       </c>
       <c r="B21" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
         <v>127101557</v>
       </c>
       <c r="B22" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
         <v>127101796</v>
       </c>
       <c r="B23" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3129,17 +3129,17 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Patrik Nygren, Sirirat Chanon</t>
+          <t>Sirirat Chanon, Patrik Nygren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127101010</v>
+        <v>127087398</v>
       </c>
       <c r="B24" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3171,14 +3171,14 @@
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Södra Bergfors , Vb</t>
+          <t>Södra Bergfors, Vb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>800532</v>
+        <v>800541</v>
       </c>
       <c r="R24" t="n">
-        <v>7176632</v>
+        <v>7176644</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3238,10 +3238,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127087398</v>
+        <v>127101010</v>
       </c>
       <c r="B25" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3273,14 +3273,14 @@
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Södra Bergfors, Vb</t>
+          <t>Södra Bergfors , Vb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>800541</v>
+        <v>800532</v>
       </c>
       <c r="R25" t="n">
-        <v>7176644</v>
+        <v>7176632</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>

--- a/artfynd/A 9093-2025 artfynd.xlsx
+++ b/artfynd/A 9093-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AY26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1932,10 +1932,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123441364</v>
+        <v>123441492</v>
       </c>
       <c r="B13" t="n">
-        <v>90977</v>
+        <v>78810</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1944,31 +1944,31 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1979,10 +1979,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>800644</v>
+        <v>800664</v>
       </c>
       <c r="R13" t="n">
-        <v>7176654</v>
+        <v>7176619</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2042,10 +2042,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123441000</v>
+        <v>123441364</v>
       </c>
       <c r="B14" t="n">
-        <v>57529</v>
+        <v>90977</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2054,35 +2054,34 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2090,10 +2089,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>800417</v>
+        <v>800644</v>
       </c>
       <c r="R14" t="n">
-        <v>7176768</v>
+        <v>7176654</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2128,17 +2127,13 @@
           <t>2025-03-21</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>hack i torraka</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2157,7 +2152,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123441038</v>
+        <v>123441000</v>
       </c>
       <c r="B15" t="n">
         <v>57529</v>
@@ -2205,10 +2200,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>800415</v>
+        <v>800417</v>
       </c>
       <c r="R15" t="n">
-        <v>7176760</v>
+        <v>7176768</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2245,7 +2240,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>hack i död gran</t>
+          <t>hack i torraka</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2272,10 +2267,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123441175</v>
+        <v>123441038</v>
       </c>
       <c r="B16" t="n">
-        <v>91030</v>
+        <v>57529</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2288,30 +2283,31 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2319,10 +2315,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>800571</v>
+        <v>800415</v>
       </c>
       <c r="R16" t="n">
-        <v>7176723</v>
+        <v>7176760</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2357,13 +2353,17 @@
           <t>2025-03-21</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>hack i död gran</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2382,10 +2382,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123441111</v>
+        <v>123441175</v>
       </c>
       <c r="B17" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2398,27 +2398,27 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -2429,10 +2429,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>800589</v>
+        <v>800571</v>
       </c>
       <c r="R17" t="n">
-        <v>7176762</v>
+        <v>7176723</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2492,10 +2492,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123441144</v>
+        <v>123441111</v>
       </c>
       <c r="B18" t="n">
-        <v>5176</v>
+        <v>78810</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2504,36 +2504,34 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2541,10 +2539,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>800585</v>
+        <v>800589</v>
       </c>
       <c r="R18" t="n">
-        <v>7176730</v>
+        <v>7176762</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2577,11 +2575,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>breda gnagspår i död gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2609,10 +2602,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123452603</v>
+        <v>123441144</v>
       </c>
       <c r="B19" t="n">
-        <v>57666</v>
+        <v>5176</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2621,33 +2614,34 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>100526</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>bobygge</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2657,10 +2651,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>800571</v>
+        <v>800585</v>
       </c>
       <c r="R19" t="n">
-        <v>7176723</v>
+        <v>7176730</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2697,7 +2691,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>litet bohål ca 3cm brett och 2,5cm högt ca 2m upp på stammen av gammal rötad gran angripen av granticka.</t>
+          <t>breda gnagspår i död gran</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2706,6 +2700,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2724,49 +2719,58 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127101303</v>
+        <v>123452603</v>
       </c>
       <c r="B20" t="n">
-        <v>98467</v>
+        <v>57666</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>bobygge</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Södra Bergfors , Vb</t>
+          <t>Bureberget, Vb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>800517</v>
+        <v>800571</v>
       </c>
       <c r="R20" t="n">
-        <v>7176618</v>
+        <v>7176723</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2793,12 +2797,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>litet bohål ca 3cm brett och 2,5cm högt ca 2m upp på stammen av gammal rötad gran angripen av granticka.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2807,7 +2816,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2819,14 +2827,14 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Sirirat Chanon, Patrik Nygren</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127101711</v>
+        <v>127101303</v>
       </c>
       <c r="B21" t="n">
         <v>98467</v>
@@ -2865,10 +2873,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>800648</v>
+        <v>800517</v>
       </c>
       <c r="R21" t="n">
-        <v>7176649</v>
+        <v>7176618</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2921,14 +2929,14 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Patrik Nygren, Sirirat Chanon</t>
+          <t>Sirirat Chanon, Patrik Nygren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127101557</v>
+        <v>127101711</v>
       </c>
       <c r="B22" t="n">
         <v>98467</v>
@@ -2958,11 +2966,7 @@
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
@@ -2971,10 +2975,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>800518</v>
+        <v>800648</v>
       </c>
       <c r="R22" t="n">
-        <v>7176638</v>
+        <v>7176649</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3034,7 +3038,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127101796</v>
+        <v>127101557</v>
       </c>
       <c r="B23" t="n">
         <v>98467</v>
@@ -3064,7 +3068,11 @@
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
@@ -3073,10 +3081,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>800652</v>
+        <v>800518</v>
       </c>
       <c r="R23" t="n">
-        <v>7176654</v>
+        <v>7176638</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3129,14 +3137,14 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Sirirat Chanon, Patrik Nygren</t>
+          <t>Patrik Nygren, Sirirat Chanon</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127087398</v>
+        <v>127101796</v>
       </c>
       <c r="B24" t="n">
         <v>98467</v>
@@ -3171,14 +3179,14 @@
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Södra Bergfors, Vb</t>
+          <t>Södra Bergfors , Vb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>800541</v>
+        <v>800652</v>
       </c>
       <c r="R24" t="n">
-        <v>7176644</v>
+        <v>7176654</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3231,14 +3239,14 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Patrik Nygren, Sirirat Chanon</t>
+          <t>Sirirat Chanon, Patrik Nygren</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127101010</v>
+        <v>127087398</v>
       </c>
       <c r="B25" t="n">
         <v>98467</v>
@@ -3273,14 +3281,14 @@
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Södra Bergfors , Vb</t>
+          <t>Södra Bergfors, Vb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>800532</v>
+        <v>800541</v>
       </c>
       <c r="R25" t="n">
-        <v>7176632</v>
+        <v>7176644</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3337,6 +3345,108 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>127101010</v>
+      </c>
+      <c r="B26" t="n">
+        <v>98467</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Södra Bergfors , Vb</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>800532</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7176632</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Bureå</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Patrik Nygren, Sirirat Chanon</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 9093-2025 artfynd.xlsx
+++ b/artfynd/A 9093-2025 artfynd.xlsx
@@ -2837,7 +2837,7 @@
         <v>127101303</v>
       </c>
       <c r="B21" t="n">
-        <v>98467</v>
+        <v>98436</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2939,7 +2939,7 @@
         <v>127101711</v>
       </c>
       <c r="B22" t="n">
-        <v>98467</v>
+        <v>98436</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3041,7 +3041,7 @@
         <v>127101557</v>
       </c>
       <c r="B23" t="n">
-        <v>98467</v>
+        <v>98436</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>127101796</v>
       </c>
       <c r="B24" t="n">
-        <v>98467</v>
+        <v>98436</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3239,17 +3239,17 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Sirirat Chanon, Patrik Nygren</t>
+          <t>Patrik Nygren, Sirirat Chanon</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127087398</v>
+        <v>127101010</v>
       </c>
       <c r="B25" t="n">
-        <v>98467</v>
+        <v>98436</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3281,14 +3281,14 @@
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Södra Bergfors, Vb</t>
+          <t>Södra Bergfors , Vb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>800541</v>
+        <v>800532</v>
       </c>
       <c r="R25" t="n">
-        <v>7176644</v>
+        <v>7176632</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3341,17 +3341,17 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Patrik Nygren, Sirirat Chanon</t>
+          <t>Sirirat Chanon, Patrik Nygren</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127101010</v>
+        <v>127087398</v>
       </c>
       <c r="B26" t="n">
-        <v>98467</v>
+        <v>98436</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3383,14 +3383,14 @@
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Södra Bergfors , Vb</t>
+          <t>Södra Bergfors, Vb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>800532</v>
+        <v>800541</v>
       </c>
       <c r="R26" t="n">
-        <v>7176632</v>
+        <v>7176644</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>

--- a/artfynd/A 9093-2025 artfynd.xlsx
+++ b/artfynd/A 9093-2025 artfynd.xlsx
@@ -1680,7 +1680,7 @@
         <v>0</v>
       </c>
       <c r="AE10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG10" t="b">
         <v>0</v>
@@ -2814,7 +2814,7 @@
         <v>0</v>
       </c>
       <c r="AE20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG20" t="b">
         <v>0</v>
@@ -2837,7 +2837,7 @@
         <v>127101303</v>
       </c>
       <c r="B21" t="n">
-        <v>98436</v>
+        <v>98467</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2939,7 +2939,7 @@
         <v>127101711</v>
       </c>
       <c r="B22" t="n">
-        <v>98436</v>
+        <v>98467</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3041,7 +3041,7 @@
         <v>127101557</v>
       </c>
       <c r="B23" t="n">
-        <v>98436</v>
+        <v>98467</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>127101796</v>
       </c>
       <c r="B24" t="n">
-        <v>98436</v>
+        <v>98467</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3239,17 +3239,17 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Patrik Nygren, Sirirat Chanon</t>
+          <t>Sirirat Chanon, Patrik Nygren</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127101010</v>
+        <v>127087398</v>
       </c>
       <c r="B25" t="n">
-        <v>98436</v>
+        <v>98467</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3281,14 +3281,14 @@
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Södra Bergfors , Vb</t>
+          <t>Södra Bergfors, Vb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>800532</v>
+        <v>800541</v>
       </c>
       <c r="R25" t="n">
-        <v>7176632</v>
+        <v>7176644</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3341,17 +3341,17 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Sirirat Chanon, Patrik Nygren</t>
+          <t>Patrik Nygren, Sirirat Chanon</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127087398</v>
+        <v>127101010</v>
       </c>
       <c r="B26" t="n">
-        <v>98436</v>
+        <v>98467</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3383,14 +3383,14 @@
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Södra Bergfors, Vb</t>
+          <t>Södra Bergfors , Vb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>800541</v>
+        <v>800532</v>
       </c>
       <c r="R26" t="n">
-        <v>7176644</v>
+        <v>7176632</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
